--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_108_R11.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_108_R11.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2382</v>
+        <v>4.8684</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3141</v>
+        <v>5.7427</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0759</v>
+        <v>-0.8743</v>
       </c>
       <c r="G2" t="n">
         <v>5.0496</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0253</v>
+        <v>-0.3951</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7978</v>
+        <v>-0.3692</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2275</v>
+        <v>-0.0259</v>
       </c>
       <c r="V2" t="n">
         <v>0.6778999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8434</v>
+        <v>3.4731</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8808</v>
+        <v>2.6449</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9627</v>
+        <v>0.8282</v>
       </c>
       <c r="G3" t="n">
         <v>2.4021</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2274</v>
+        <v>0.8571</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7275</v>
+        <v>0.4916</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4999</v>
+        <v>0.3655</v>
       </c>
       <c r="V3" t="n">
         <v>0.6778999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7605</v>
+        <v>3.4299</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8144</v>
+        <v>4.1814</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0539</v>
+        <v>-0.7514</v>
       </c>
       <c r="G4" t="n">
         <v>2.5994</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2333</v>
+        <v>-0.0973</v>
       </c>
       <c r="T4" t="n">
-        <v>0.767</v>
+        <v>0.134</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5337</v>
+        <v>-0.2313</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. TONUT</t>
+          <t>N. MANNION</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.083</v>
+        <v>0.0291</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2443</v>
+        <v>-0.1195</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.1613</v>
+        <v>0.1486</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8722</v>
+        <v>0.2698</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5175</v>
+        <v>-1.9351</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3547</v>
+        <v>2.2049</v>
       </c>
       <c r="J5" t="n">
-        <v>2.063</v>
+        <v>0.8279</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9158</v>
+        <v>-1.2198</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1472</v>
+        <v>2.0476</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1908</v>
+        <v>-0.5581</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3983</v>
+        <v>-0.7153</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2075</v>
+        <v>0.1573</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8913</v>
+        <v>0.4551</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.4443</v>
       </c>
       <c r="U5" t="n">
-        <v>0.156</v>
+        <v>0.0108</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.8223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. MANNION</t>
+          <t>S. TONUT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4256</v>
+        <v>-0.1193</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4734</v>
+        <v>3.0084</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0477</v>
+        <v>-3.1277</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2698</v>
+        <v>0.8722</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9351</v>
+        <v>0.5175</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2049</v>
+        <v>0.3547</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8279</v>
+        <v>2.063</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2198</v>
+        <v>1.9158</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0476</v>
+        <v>0.1472</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5581</v>
+        <v>-1.1908</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7153</v>
+        <v>-1.3983</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1573</v>
+        <v>0.2075</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0004</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0905</v>
+        <v>0.4995</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0901</v>
+        <v>0.1896</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1806</v>
+        <v>-0.5841</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6932</v>
+        <v>-0.2647</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4874</v>
+        <v>-0.3194</v>
       </c>
       <c r="G7" t="n">
         <v>1.4674</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6506</v>
+        <v>-0.054</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4991</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1516</v>
+        <v>0.0165</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1418</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. BOLMARO</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3158</v>
+        <v>-1.0225</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5580000000000001</v>
+        <v>0.3724</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7578</v>
+        <v>-1.3949</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5518</v>
+        <v>-0.6744</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7493</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1975</v>
+        <v>-1.2112</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.24</v>
+        <v>0.891</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4411</v>
+        <v>0.9915</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2011</v>
+        <v>-0.1005</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3119</v>
+        <v>-1.5654</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3082</v>
+        <v>-0.4547</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0037</v>
+        <v>-1.1107</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7721</v>
+        <v>-0.0619</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0736</v>
+        <v>-0.2867</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6985</v>
+        <v>0.2247</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>L. BOLMARO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4846</v>
+        <v>-2.3686</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0561</v>
+        <v>-1.0731</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4285</v>
+        <v>-1.2955</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6744</v>
+        <v>-1.5518</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5368000000000001</v>
+        <v>-1.7493</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2112</v>
+        <v>0.1975</v>
       </c>
       <c r="J9" t="n">
-        <v>0.891</v>
+        <v>-0.24</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9915</v>
+        <v>-1.4411</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1005</v>
+        <v>1.2011</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5654</v>
+        <v>-1.3119</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4547</v>
+        <v>-0.3082</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1107</v>
+        <v>-1.0037</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.4639</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.9278</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.1598</v>
-      </c>
       <c r="S9" t="n">
-        <v>-0.5241</v>
+        <v>0.7194</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7151999999999999</v>
+        <v>0.5586</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1911</v>
+        <v>0.1608</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.4787</v>
+        <v>-6.2929</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3223</v>
+        <v>-3.9684</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1565</v>
+        <v>-2.3245</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5545</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0215</v>
+        <v>0.2074</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2003</v>
+        <v>0.1535</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2219</v>
+        <v>0.0538</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9304</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.039800000000001</v>
+        <v>1.413099999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>10.1506</v>
+        <v>10.5241</v>
       </c>
       <c r="F11" t="n">
         <v>-9.110900000000001</v>
@@ -1300,7 +1300,7 @@
         <v>-5.850000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.8211</v>
+        <v>-5.821099999999999</v>
       </c>
       <c r="P11" t="n">
         <v>-4.6391</v>
@@ -1312,10 +1312,10 @@
         <v>8.118499999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>1.946</v>
+        <v>2.3197</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1816</v>
+        <v>1.5551</v>
       </c>
       <c r="U11" t="n">
         <v>0.7645</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.538</v>
+        <v>8.713100000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>8.484299999999999</v>
+        <v>8.366400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0537</v>
+        <v>0.3467</v>
       </c>
       <c r="G12" t="n">
         <v>5.7578</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6721</v>
+        <v>0.8472</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3462</v>
+        <v>0.2282</v>
       </c>
       <c r="U12" t="n">
-        <v>0.326</v>
+        <v>0.619</v>
       </c>
       <c r="V12" t="n">
         <v>0.2525</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1832</v>
+        <v>6.2727</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9812</v>
+        <v>7.2171</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7979</v>
+        <v>-0.9444</v>
       </c>
       <c r="G13" t="n">
         <v>1.0713</v>
@@ -1468,13 +1468,13 @@
         <v>2.0876</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2618</v>
+        <v>0.8276</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2434</v>
+        <v>-0.0075</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0184</v>
+        <v>0.8351</v>
       </c>
       <c r="V13" t="n">
         <v>2.2862</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.195</v>
+        <v>1.6668</v>
       </c>
       <c r="E14" t="n">
-        <v>3.746</v>
+        <v>2.3306</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.551</v>
+        <v>-0.6639</v>
       </c>
       <c r="G14" t="n">
         <v>-0.4398</v>
@@ -1546,13 +1546,13 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1013</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.628</v>
+        <v>0.2126</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5266999999999999</v>
+        <v>0.3605</v>
       </c>
       <c r="V14" t="n">
         <v>0.1418</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4294</v>
+        <v>0.0248</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.4098</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4522</v>
+        <v>-0.3849</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4172</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2926</v>
+        <v>-0.112</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5623</v>
+        <v>0.0905</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2697</v>
+        <v>-0.2025</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.763</v>
+        <v>-0.2804</v>
       </c>
       <c r="E16" t="n">
         <v>-1.0556</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2926</v>
+        <v>0.7751</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0323</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6585</v>
+        <v>-0.1759</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1415</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5171</v>
+        <v>-0.0345</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0957</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4551</v>
+        <v>0.0167</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6405</v>
+        <v>-0.877</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8759</v>
@@ -1780,13 +1780,13 @@
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.31</v>
+        <v>-0.0747</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5149</v>
+        <v>-0.0431</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7951</v>
+        <v>-0.0316</v>
       </c>
       <c r="V17" t="n">
         <v>0.3943</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. LEE</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2606</v>
+        <v>-1.5304</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3502</v>
+        <v>-0.4914</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9104</v>
+        <v>-1.039</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5348000000000001</v>
+        <v>0.1735</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4813</v>
+        <v>-2.6805</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0535</v>
+        <v>2.8541</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0336</v>
+        <v>2.0713</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0336</v>
+        <v>-2.2582</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4.3295</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5684</v>
+        <v>-1.8978</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5149</v>
+        <v>-0.4223</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0535</v>
+        <v>-1.4755</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4938</v>
+        <v>-0.2221</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.224</v>
+        <v>-0.3851</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2697</v>
+        <v>0.163</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>S. LEE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3776</v>
+        <v>-2.1933</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8453000000000001</v>
+        <v>-1.3502</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5323</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1735</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.6805</v>
+        <v>-0.4813</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8541</v>
+        <v>-0.0535</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0713</v>
+        <v>0.0336</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.2582</v>
+        <v>0.0336</v>
       </c>
       <c r="L19" t="n">
-        <v>4.3295</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8978</v>
+        <v>-0.5684</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4223</v>
+        <v>-0.5149</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4755</v>
+        <v>-0.0535</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.6237</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0693</v>
+        <v>-0.4266</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7389</v>
+        <v>-0.224</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3304</v>
+        <v>-0.2025</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5413</v>
+        <v>-2.8374</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0254</v>
+        <v>-1.9075</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5159</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-5.5076</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8219</v>
+        <v>0.5258</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.326</v>
+        <v>-0.208</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1479</v>
+        <v>0.7339</v>
       </c>
       <c r="V20" t="n">
         <v>2.1444</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.3475</v>
+        <v>-6.0836</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.7147</v>
+        <v>-3.889</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6328</v>
+        <v>-2.1946</v>
       </c>
       <c r="G21" t="n">
         <v>-5.0748</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0407</v>
+        <v>0.2232</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1123</v>
+        <v>-0.2867</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0716</v>
+        <v>0.5098</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5361</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.040100000000002</v>
+        <v>2.891900000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>9.646800000000002</v>
+        <v>9.6469</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.6867</v>
+        <v>-6.755099999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-7.8798</v>
@@ -2170,13 +2170,13 @@
         <v>12.7575</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9462</v>
+        <v>1.9856</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7645000000000002</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1816</v>
+        <v>2.7502</v>
       </c>
       <c r="V22" t="n">
         <v>4.146999999999999</v>
